--- a/data/02_Daily_Sheets/Expressions_2026-07-22.xlsx
+++ b/data/02_Daily_Sheets/Expressions_2026-07-22.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CHI-20260722-001</t>
+          <t>CHI-20260722-018</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>得不偿失</t>
+          <t>心心念念</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -491,29 +491,29 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>débùchángshī</t>
+          <t>xīn xīn niàn niàn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>얻는 것보다 잃는 것이 많다, 득보다 실이 크다</t>
+          <t>간절히 바라다, 늘 마음속으로 염원하다</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>단기적인 이익을 위해 장기적인 관계를 망치는 것은 결국 얻는 것보다 잃는 것이 많을 것입니다.</t>
+          <t>独立整洁的学习空间是很多困境青少年心心念念的心愿。</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>为了省一点小钱而浪费大量时间，真是得不偿失。</t>
+          <t>她终于拿到了心心念念的名企实习录取通知书。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CHI-20260722-002</t>
+          <t>CHI-20260722-019</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>心里有数</t>
+          <t>不问青红皂白</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -538,29 +538,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>xīnli yǒushù</t>
+          <t>bù wèn qīng hóng zào bái</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>잘 알고 있다, 속으로 헤아리고 있다, 짐작하고 있다</t>
+          <t>사정이나 앞뒤 맥락을 따지지도 않고 무작정</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>프로젝트 진행 상황에 대해 그는 이미 잘 알고 있을 것입니다.</t>
+          <t>海上一有风吹草动，有人就不问青红皂白地把责任推给别人。</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>虽然他没说，但我知道他心里有数，一切都在计划中。</t>
+          <t>你不能不问青红皂白就批评下属，先听听他的解释。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CHI-20260722-003</t>
+          <t>CHI-20260722-020</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>一窍不通</t>
+          <t>风吹草动</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -585,29 +585,29 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>yīqiàobùtōng</t>
+          <t>fēng chuī cǎo dòng</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>문외한이다, 전혀 알지 못하다</t>
+          <t>미세한 변화나 소문, 조그만 기척</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>저는 경제학에 대해 전혀 알지 못해서 관련 기사를 읽어도 이해하기 어렵습니다.</t>
+          <t>哪怕海面上有一点风吹草动，某些媒体就会过度炒作。</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>我对电脑维修一窍不通，完全不知道该怎么办。</t>
+          <t>行业内一有风吹草动，很多投资者就会变得非常敏感。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CHI-20260722-004</t>
+          <t>CHI-20260722-021</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>封顶</t>
+          <t>攀比</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -632,29 +632,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>fēng dǐng</t>
+          <t>pān bǐ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>(건물 등) 골조 공사를 마치다, 상량하다; (수치 등이) 최고치에 달하다</t>
+          <t>남과 비교하며 과소비하거나 허세를 부리다</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>副中心又一家国企总部大楼主体封顶！</t>
+          <t>高考结束后，不少学生盲目攀比买高档电子产品，增加了家长的负担。</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>经过两年的建设，新博物馆的主体工程终于顺利封顶了。</t>
+          <t>年轻人消费要理性，不要盲目和别人攀比。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHI-20260722-005</t>
+          <t>CHI-20260722-022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -669,39 +669,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>夯实</t>
+          <t>掏腰包</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>동사</t>
+          <t>관용구</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>hāng shí</t>
+          <t>tāo yāo bāo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>(기초를) 다지다, 튼튼히 하다, 공고히 하다</t>
+          <t>자기 지갑을 열다, 사비를 들이다</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>双权威绿标加持，大王椰持续夯实家居板材健康底色.</t>
+          <t>为了给高考毕业的孩子的“成人礼”买单，许多父母不得不掏腰包。</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>我们要持续夯实技术基础，才能在激烈的市场竞争中立于不败之地。</t>
+          <t>这次部门聚会的费用全部由主管掏腰包了。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHI-20260722-006</t>
+          <t>CHI-20260722-023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -716,39 +716,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>直面</t>
+          <t>铺路</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>동사</t>
+          <t>이합사</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>zhí miàn</t>
+          <t>pū lù</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>(문제 등을) 정면으로 마주하다, 직시하다</t>
+          <t>미래를 위해 기반을 다지다, 길을 터주다</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>首期直面“家底”与“短...”</t>
+          <t>政府推进就业保障政策，就是为了给年轻人的未来发展铺路。</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>面对经济下行的压力，我们必须直面挑战，积极寻求解决方案。</t>
+          <t>父母辛辛苦苦工作，就是为了给孩子的未来铺路。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CHI-20260722-007</t>
+          <t>CHI-20260722-024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -763,39 +763,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>增资</t>
+          <t>摸底</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>이합사</t>
+          <t>동사</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>zēng zī</t>
+          <t>mō dǐ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>(회사, 기업 등이) 자본금을 늘리다, 증자하다</t>
+          <t>사전에 정황, 실태, 실력을 사전에 조사하거나 파악하다</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>大连重工：全资子公司增资完成工商变更登记.</t>
+          <t>相关部门在出台新政策前，对新就业形态劳动者的人数进行了摸底。</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>为了扩大生产规模，公司决定向股东募集资金进行增资。</t>
+          <t>开会前，我们要对客户的需求做一个详细的摸底。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CHI-20260722-008</t>
+          <t>CHI-20260722-025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -810,39 +810,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>引进人才</t>
+          <t>散心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>구어</t>
+          <t>이합사</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>yǐn jìn rén cái</t>
+          <t>sàn xīn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인재를 유치하다/영입하다</t>
+          <t>답답한 마음을 달래다, 머리를 식히다</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>上海新金山投资控股集团有限公司面向社会引进专业技术人才2名.</t>
+          <t>高考结束后，很多考生选择出去旅游散心，缓解长期的压力。</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>为了提升科研实力，我们大学每年都致力于引进高水平人才。</t>
+          <t>工作太累了，周末我想去郊区散散心。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHI-20260722-009</t>
+          <t>CHI-20260722-026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -857,39 +857,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>滋事挑衅</t>
+          <t>交心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>관용구</t>
+          <t>이합사</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>zī shì tiǎo xìn</t>
+          <t>jiāo xīn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>문제를 일으키고 도발하다</t>
+          <t>솔직하게 속마음을 나누다</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>外交部：敦促菲方立即停止海上滋事挑衅和...</t>
+          <t>社区志愿者走访困境家庭，与青少年交心，了解他们的真实想法。</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>任何国家都无权在他国领土上滋事挑衅。</t>
+          <t>我和他认识多年了，是非常交心的朋友。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CHI-20260722-010</t>
+          <t>CHI-20260722-027</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>规划建设</t>
+          <t>砸钱</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -914,29 +914,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>guī huà jiàn shè</t>
+          <t>zá qián</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>계획하고 건설하다</t>
+          <t>거침없이 많은 돈을 쏟아붓다</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>系统推进“六张网”规划建设，国常会再部署.</t>
+          <t>不少商家瞄准准考生市场，靠砸钱宣传来吸引消费者。</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>城市发展需要长远的规划建设，才能避免盲目扩张。</t>
+          <t>这个项目光靠砸钱是没用的，关键是要有好的产品设计。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CHI-20260722-011</t>
+          <t>CHI-20260722-028</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>扩大投资</t>
+          <t>买单</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -961,29 +961,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>kuò dà tóu zī</t>
+          <t>mǎi dān</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>투자를 확대하다</t>
+          <t>계산하다, (결과나 실수에 대해) 책임지다</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>作为今年扩大有效投资的重要发力点，“六张网”规划建设正迎来密集的政策部署.</t>
+          <t>盲目消费的后果，最终还是要由学生和家长自己买单。</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>政府鼓励企业扩大投资，以促进经济增长和创造就业机会。</t>
+          <t>我们做出的每一个决策，都必须自己去买单。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CHI-20260722-012</t>
+          <t>CHI-20260722-029</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -998,39 +998,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>失控</t>
+          <t>打下手</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>이합사</t>
+          <t>관용구</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>shī kòng</t>
+          <t>dǎ xià shǒu</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>통제 불능이 되다, 제어력을 상실하다</t>
+          <t>보조 역할을 하다, 옆에서 수발을 들다</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>失控的监护“外包”：孩子被送特训机构之后.</t>
+          <t>新进公司的实习生一般先从打下手开始，慢慢熟悉业务。</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>如果不及时采取措施，疫情可能会彻底失控。</t>
+          <t>今天做饭你主厨，我在旁边给你打下手。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CHI-20260722-013</t>
+          <t>CHI-20260722-030</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1045,39 +1045,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>着手</t>
+          <t>推波助澜</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>동사</t>
+          <t>관용구</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>zhuó shǒu</t>
+          <t>tuī bō zhù lán</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>착수하다, 시작하다</t>
+          <t>부추기다, (일의 상황을) 한층 더 부채질하다</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(새로운 사업/프로젝트 시작 맥락에서 유추)</t>
+          <t>部分商家为了增加销量，在社交平台上推波助澜，炒作过度消费的风气。</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>新项目马上要启动了，我们得尽快着手准备。</t>
+          <t>网络上的不实言论对这次公关危机起到了推波助澜的反效果。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CHI-20260722-014</t>
+          <t>CHI-20260722-031</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1092,39 +1092,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>摆脱</t>
+          <t>兜底</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>동사</t>
+          <t>구어</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>bǎi tuō</t>
+          <t>dōu dǐ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>벗어나다, 떨쳐버리다</t>
+          <t>최후의 보장을 하다, 끝까지 책임지고 처리해주다</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(어려운 상황이나 제약에서 벗어나는 맥락에서 유추)</t>
+          <t>政府出台了保障政策，为新就业形态劳动者的基本权益兜底。</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>他努力工作，终于摆脱了贫困的生活。</t>
+          <t>你放手去干吧，万一出了什么问题由我们团队来兜底。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CHI-20260722-015</t>
+          <t>CHI-20260722-032</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1139,39 +1139,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>达成协议</t>
+          <t>提上日程</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>구어</t>
+          <t>관용구</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>dá chéng xié yì</t>
+          <t>tí shàng rì chéng</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>협의에 도달하다, 합의를 이루다</t>
+          <t>일정에 올리다, 본격적으로 추진을 시작하다</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(기업 간 협력, 국제 관계 등의 맥락에서 유추)</t>
+          <t>随着新一轮改革推行，个人养老金制度的细则落地已被提上日程。</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>经过多轮谈判，双方终于就贸易问题达成了协议。</t>
+          <t>公司决定将新产品的海外推广计划正式提上日程。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CHI-20260722-016</t>
+          <t>CHI-20260722-033</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,39 +1186,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>拭目以待</t>
+          <t>支招</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>관용구</t>
+          <t>구어</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>shì mù yǐ dài</t>
+          <t>zhī zhāo</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>눈을 닦고 기다리다; (결과를) 기대하며 지켜보다</t>
+          <t>아이디어를 주다, 해결책을 제시해 주다</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(발표된 정책이나 프로젝트의 결과를 기대하는 맥락에서 유추)</t>
+          <t>针对困境学子的求职难题，多位行业专家现场为他们支招。</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>这部电影备受期待，观众们都拭目以待它的上映。</t>
+          <t>面对这么棘手的客户投诉，老同事给刚入职的我支了几招。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CHI-20260722-017</t>
+          <t>CHI-20260722-034</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1233,32 +1233,79 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>顺理成章</t>
+          <t>明眼人</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>míng yǎn rén</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>통찰력 있는 사람, 상황을 똑똑히 알아채는 사리 밝은 사람</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>明眼人都能看得出，这次策略调整是为了顺应未来的政策导向。</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>这明显是个商业陷阱，稍有经验的明眼人一扫就能看穿。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CHI-20260722-035</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Scraped_News</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>见缝插针</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>관용구</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>shùn lǐ chéng zhāng</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>이치에 맞아 당연하다, 순리대로 이루어지다</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(특정 결과나 상황이 자연스러운 흐름에 따라 발생한다는 맥락에서 유추)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>他的努力工作와 우수한 성과를 고려할 때, 승진은 순리성장한 일이다.</t>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>jiàn fèng chā zhēn</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>짬을 내다, 바쁜 와중에도 틈을 활용하다</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>很多职场年轻人见缝插针地利用日常碎片时间学习第二外语。</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>出差行程安排得非常紧，他只能见缝插针地在高铁上批改文件。</t>
         </is>
       </c>
     </row>
